--- a/stories/arbres/TREE-FAM-001.xlsx
+++ b/stories/arbres/TREE-FAM-001.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Zoé est dans le train, avec papa. Maman les rejoint à la gare. Zoé a fait une petite bêtise. Un cube est tombé. Papa dit : on raconte à papa ou maman ce qui s'est passé.</t>
+          <t>Zoé est dans le train, avec papa. Maman les rejoint à la gare. Zoé a fait une petite bêtise. Un cube est tombé. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé est dans le train, avec papa. Maman les rejoint à la gare. Zoé a fait une petite bêtise. Un cube est tombé.
+papa|On raconte à papa ou maman ce qui s'est passé.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1677,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le train, Zoé a sorti les cubes. Un cube a roulé sous le siège. Zoé a un serrement. Elle raconte à papa. Papa écoute. On raconte à papa ou maman ce qui s'est passé.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On raconte à papa ou maman ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On raconte à papa ou maman. Zoé respire. Papa est là. On raconte à papa ou maman ce qui s'est passé.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2207,7 +2255,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Papa tend une pomme. Zoé raconte encore : le cube a roulé. On raconte à papa ou maman. Papa dit : je t'écoute. Papa montre le geste, lentement. On raconte à papa ou maman ce qui s'est passé.</t>
+          <t>Papa tend une pomme. Zoé raconte encore : le cube a roulé. On raconte à papa ou maman. Je t'écoute. Papa montre le geste, lentement. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2345,6 +2393,12 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Papa tend une pomme. Zoé raconte encore : le cube a roulé. On raconte à papa ou maman.
+papa|Je t'écoute. Papa montre le geste, lentement. On raconte à papa ou maman ce qui s'est passé.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2585,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2752,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi les cubes. Puis une pomme. Puis le chat. La couverture est douce. Maman n'est pas loin. Zoé les rejoint. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2919,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3086,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'arrête près de le chien. une pomme est rangé. Les chaussures font toc toc. Zoé caresse le doudou. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3253,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3420,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé se souvient de les cubes. Et de une pomme. Et de la poule. On écoute jusqu'au bout. Zoé s'assoit près de papa. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3587,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3616,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Papa tend un yaourt. Zoé raconte encore : le cube a roulé. On raconte à papa ou maman. Papa dit : je t'écoute. Papa dit : je suis là. On raconte à papa ou maman ce qui s'est passé.</t>
+          <t>Papa tend un yaourt. Zoé raconte encore : le cube a roulé. On raconte à papa ou maman. Je t'écoute. Je suis là. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3754,13 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Papa tend un yaourt. Zoé raconte encore : le cube a roulé. On raconte à papa ou maman.
+papa|Je t'écoute.
+papa|Je suis là. On raconte à papa ou maman ce qui s'est passé.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3947,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4013,6 +4114,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le chat. Après un yaourt. Près de les cubes. Zoé s'arrête. Un chat miaule une fois. Zoé pose sa tête un moment. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4281,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4448,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé range un yaourt. le chien reste près de les cubes. On dit merci. Zoé souffle, puis sourit à papa. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4615,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4523,7 +4644,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>la poule est là. un yaourt aussi. les cubes reste dans le souvenir. Un panier est posé sur le banc. Zoé plie un pull. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+          <t>La poule est là. un yaourt aussi. les cubes reste dans le souvenir. Un panier est posé sur le banc. Zoé plie un pull. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4661,6 +4782,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|La poule est là. un yaourt aussi. les cubes reste dans le souvenir. Un panier est posé sur le banc. Zoé plie un pull. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4949,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4847,7 +4978,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Papa tend un morceau de pain. Zoé raconte encore : le cube a roulé. On raconte à papa ou maman. Papa dit : je t'écoute. Papa reste tout près. On raconte à papa ou maman ce qui s'est passé.</t>
+          <t>Papa tend un morceau de pain. Zoé raconte encore : le cube a roulé. On raconte à papa ou maman. Je t'écoute. Papa reste tout près. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -4985,6 +5116,12 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Papa tend un morceau de pain. Zoé raconte encore : le cube a roulé. On raconte à papa ou maman.
+papa|Je t'écoute. Papa reste tout près. On raconte à papa ou maman ce qui s'est passé.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5308,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5475,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le chat. un morceau de pain est rangé. les cubes est fini. Une pomme brille un peu. Zoé range les cubes dans sa tête, comme un souvenir. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5642,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5809,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le chien. Zoé pose un morceau de pain. les cubes est derrière. Un linge sèche à l'air. Zoé boit une gorgée d'eau. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5976,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6143,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé montre la poule. Papa a vu les cubes. Et un morceau de pain. Ça sent le pain chaud. Zoé sourit. Papa sourit aussi. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6310,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6305,6 +6477,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le train, Zoé a ouvert le livre. Une page s'est un peu froissée. Zoé le dit. Elle raconte à papa. Maman aura la même histoire, tout à l'heure. On raconte à papa ou maman.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6481,6 +6658,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Une bêtise : on fait quoi ?</t>
         </is>
       </c>
     </row>
@@ -6649,6 +6831,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On raconte à papa ou maman. Zoé retient le geste. Papa sourit. On raconte à papa ou maman ce qui s'est passé.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6835,6 +7022,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6859,7 +7051,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Papa tend une pomme. Zoé raconte : la page s'est froissée. On raconte à papa ou maman. Papa dit : merci de raconter. Papa dit : je suis là. On raconte à papa ou maman ce qui s'est passé.</t>
+          <t>Papa tend une pomme. Zoé raconte : la page s'est froissée. On raconte à papa ou maman. Merci de raconter. Je suis là. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -6997,6 +7189,13 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Papa tend une pomme. Zoé raconte : la page s'est froissée. On raconte à papa ou maman.
+papa|Merci de raconter.
+papa|Je suis là. On raconte à papa ou maman ce qui s'est passé.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7183,6 +7382,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7345,6 +7549,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi le livre. Puis une pomme. Puis le chat. Une cloche tinte, tout loin. Zoé essuie ses mains. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7507,6 +7716,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7669,6 +7883,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'arrête près de le chien. une pomme est rangé. Le savon sent bon. Zoé marche près de papa. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7831,6 +8050,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7993,6 +8217,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé se souvient de le livre. Et de une pomme. Et de la poule. Une tasse cliquette. Zoé range encore un peu, près de papa. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8155,6 +8384,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8179,7 +8413,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Papa tend un yaourt. Zoé raconte : la page s'est froissée. On raconte à papa ou maman. Papa dit : merci de raconter. Papa reste tout près. On raconte à papa ou maman ce qui s'est passé.</t>
+          <t>Papa tend un yaourt. Zoé raconte : la page s'est froissée. On raconte à papa ou maman. Merci de raconter. Papa reste tout près. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8317,6 +8551,12 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Papa tend un yaourt. Zoé raconte : la page s'est froissée. On raconte à papa ou maman.
+papa|Merci de raconter. Papa reste tout près. On raconte à papa ou maman ce qui s'est passé.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8503,6 +8743,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8665,6 +8910,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le chat. Après un yaourt. Près de le livre. Zoé s'arrête. On souffle doucement. Zoé pose un yaourt à sa place. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8827,6 +9077,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8989,6 +9244,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé range un yaourt. le chien reste près de le livre. Un galet est encore chaud. Zoé tend le chien à maman. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9151,6 +9411,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9175,7 +9440,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>la poule est là. un yaourt aussi. le livre reste dans le souvenir. On entend un oiseau. Zoé dit : j'ai appris. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+          <t>La poule est là. un yaourt aussi. le livre reste dans le souvenir. On entend un oiseau. J'ai appris. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9313,6 +9578,13 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|La poule est là. un yaourt aussi. le livre reste dans le souvenir. On entend un oiseau.
+enfant-f|J'ai appris. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman.
+narrateur|Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9475,6 +9747,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9499,7 +9776,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Papa tend un morceau de pain. Zoé raconte : la page s'est froissée. On raconte à papa ou maman. Papa dit : merci de raconter. Papa montre le geste, lentement. On raconte à papa ou maman ce qui s'est passé.</t>
+          <t>Papa tend un morceau de pain. Zoé raconte : la page s'est froissée. On raconte à papa ou maman. Merci de raconter. Papa montre le geste, lentement. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9637,6 +9914,12 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Papa tend un morceau de pain. Zoé raconte : la page s'est froissée. On raconte à papa ou maman.
+papa|Merci de raconter. Papa montre le geste, lentement. On raconte à papa ou maman ce qui s'est passé.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9823,6 +10106,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9985,6 +10273,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le chat. un morceau de pain est rangé. le livre est fini. On se tient la main. Zoé range la tasse. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10147,6 +10440,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10309,6 +10607,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le chien. Zoé pose un morceau de pain. le livre est derrière. On rit un peu. Zoé ferme le sac. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10471,6 +10774,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10633,6 +10941,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé montre la poule. Papa a vu le livre. Et un morceau de pain. La lumière est claire. Zoé serre la main de papa. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10795,6 +11108,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10819,7 +11137,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Dans le train, Zoé a sorti la dînette. Une tasse a tapé le sol. Zoé raconte à papa. Papa dit : merci de raconter. On raconte à papa ou maman ce qui s'est passé.</t>
+          <t>Dans le train, Zoé a sorti la dînette. Une tasse a tapé le sol. Zoé raconte à papa. Merci de raconter. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10957,6 +11275,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le train, Zoé a sorti la dînette. Une tasse a tapé le sol. Zoé raconte à papa.
+papa|Merci de raconter. On raconte à papa ou maman ce qui s'est passé.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11133,6 +11457,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|On cache, ou on raconte ?</t>
         </is>
       </c>
     </row>
@@ -11301,6 +11630,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On raconte à papa ou maman. Zoé hoche la tête. On continue, avec papa. On raconte à papa ou maman ce qui s'est passé.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11487,6 +11821,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11511,7 +11850,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Papa tend une pomme. Zoé raconte : la tasse a tapé le sol. On raconte à papa ou maman. Papa dit : je suis là. Papa reste tout près. On raconte à papa ou maman ce qui s'est passé.</t>
+          <t>Papa tend une pomme. Zoé raconte : la tasse a tapé le sol. On raconte à papa ou maman. Je suis là. Papa reste tout près. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11649,6 +11988,12 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Papa tend une pomme. Zoé raconte : la tasse a tapé le sol. On raconte à papa ou maman.
+papa|Je suis là. Papa reste tout près. On raconte à papa ou maman ce qui s'est passé.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11835,6 +12180,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11997,6 +12347,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé a choisi la dînette. Puis une pomme. Puis le chat. Le vent est doux. Zoé ferme la porte, tout doux. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12159,6 +12514,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12321,6 +12681,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé s'arrête près de le chien. une pomme est rangé. Une feuille tombe. Zoé prend la main de papa. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12483,6 +12848,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12645,6 +13015,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé se souvient de la dînette. Et de une pomme. Et de la poule. Une chaussette est encore sablée. Zoé répète tout bas le geste. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12807,6 +13182,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12831,7 +13211,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Papa tend un yaourt. Zoé raconte : la tasse a tapé le sol. On raconte à papa ou maman. Papa dit : je suis là. Papa montre le geste, lentement. On raconte à papa ou maman ce qui s'est passé.</t>
+          <t>Papa tend un yaourt. Zoé raconte : la tasse a tapé le sol. On raconte à papa ou maman. Je suis là. Papa montre le geste, lentement. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -12969,6 +13349,12 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Papa tend un yaourt. Zoé raconte : la tasse a tapé le sol. On raconte à papa ou maman.
+papa|Je suis là. Papa montre le geste, lentement. On raconte à papa ou maman ce qui s'est passé.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13155,6 +13541,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13317,6 +13708,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le chat. Après un yaourt. Près de la dînette. Zoé s'arrête. On attend son tour. Zoé montre le chat à papa. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13479,6 +13875,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13641,6 +14042,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé range un yaourt. le chien reste près de la dînette. Un vélo passe au loin. Zoé écoute papa encore une fois. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13803,6 +14209,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13827,7 +14238,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>la poule est là. un yaourt aussi. la dînette reste dans le souvenir. On range un objet. Zoé enfile ses chaussons. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+          <t>La poule est là. un yaourt aussi. la dînette reste dans le souvenir. On range un objet. Zoé enfile ses chaussons. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13965,6 +14376,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|La poule est là. un yaourt aussi. la dînette reste dans le souvenir. On range un objet. Zoé enfile ses chaussons. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14127,6 +14543,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14151,7 +14572,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Papa tend un morceau de pain. Zoé raconte : la tasse a tapé le sol. On raconte à papa ou maman. Papa dit : je suis là. Papa dit : je suis là. On raconte à papa ou maman ce qui s'est passé.</t>
+          <t>Papa tend un morceau de pain. Zoé raconte : la tasse a tapé le sol. On raconte à papa ou maman. Je suis là. Je suis là. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14289,6 +14710,13 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Papa tend un morceau de pain. Zoé raconte : la tasse a tapé le sol. On raconte à papa ou maman.
+papa|Je suis là.
+papa|Je suis là. On raconte à papa ou maman ce qui s'est passé.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14475,6 +14903,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14637,6 +15070,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé rejoint le chat. un morceau de pain est rangé. la dînette est fini. L'eau coule, tout petit bruit. Zoé raccroche un linge. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14799,6 +15237,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14961,6 +15404,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de le chien. Zoé pose un morceau de pain. la dînette est derrière. Un ballon s'immobilise. Zoé dit merci à papa. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15123,6 +15571,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15285,6 +15738,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Zoé montre la poule. Papa a vu la dînette. Et un morceau de pain. Un crochet tient bien le manteau. Zoé chuchote : c'est fini. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15447,6 +15905,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15465,7 +15928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15482,6 +15945,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-FAM-001.xlsx
+++ b/stories/arbres/TREE-FAM-001.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 papa|On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
           <t>narrateur|Dans le train, Zoé a sorti les cubes. Un cube a roulé sous le siège. Zoé a un serrement. Elle raconte à papa. Papa écoute. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|On raconte à papa ou maman ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. On raconte à papa ou maman. Zoé respire. Papa est là. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2399,6 +2410,7 @@
 papa|Je t'écoute. Papa montre le geste, lentement. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2588,6 +2600,11 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -2757,6 +2774,7 @@
           <t>narrateur|Zoé a choisi les cubes. Puis une pomme. Puis le chat. La couverture est douce. Maman n'est pas loin. Zoé les rejoint. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2924,6 +2942,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3091,6 +3110,11 @@
           <t>narrateur|Zoé s'arrête près de le chien. une pomme est rangé. Les chaussures font toc toc. Zoé caresse le doudou. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3258,6 +3282,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3425,6 +3450,7 @@
           <t>narrateur|Zoé se souvient de les cubes. Et de une pomme. Et de la poule. On écoute jusqu'au bout. Zoé s'assoit près de papa. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3592,6 +3618,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3761,6 +3788,7 @@
 papa|Je suis là. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3950,6 +3978,11 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -4119,6 +4152,7 @@
           <t>narrateur|Avec le chat. Après un yaourt. Près de les cubes. Zoé s'arrête. Un chat miaule une fois. Zoé pose sa tête un moment. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4286,6 +4320,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4453,6 +4488,11 @@
           <t>narrateur|Zoé range un yaourt. le chien reste près de les cubes. On dit merci. Zoé souffle, puis sourit à papa. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4620,6 +4660,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4787,6 +4828,7 @@
           <t>narrateur|La poule est là. un yaourt aussi. les cubes reste dans le souvenir. Un panier est posé sur le banc. Zoé plie un pull. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4954,6 +4996,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5122,6 +5165,7 @@
 papa|Je t'écoute. Papa reste tout près. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5311,6 +5355,11 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -5480,6 +5529,7 @@
           <t>narrateur|Zoé rejoint le chat. un morceau de pain est rangé. les cubes est fini. Une pomme brille un peu. Zoé range les cubes dans sa tête, comme un souvenir. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5647,6 +5697,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5814,6 +5865,11 @@
           <t>narrateur|Près de le chien. Zoé pose un morceau de pain. les cubes est derrière. Un linge sèche à l'air. Zoé boit une gorgée d'eau. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5981,6 +6037,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6148,6 +6205,7 @@
           <t>narrateur|Zoé montre la poule. Papa a vu les cubes. Et un morceau de pain. Ça sent le pain chaud. Zoé sourit. Papa sourit aussi. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6315,6 +6373,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6482,6 +6541,7 @@
           <t>narrateur|Dans le train, Zoé a ouvert le livre. Une page s'est un peu froissée. Zoé le dit. Elle raconte à papa. Maman aura la même histoire, tout à l'heure. On raconte à papa ou maman.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6665,6 +6725,7 @@
           <t>narrateur|Une bêtise : on fait quoi ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6836,6 +6897,7 @@
           <t>narrateur|Oui. On raconte à papa ou maman. Zoé retient le geste. Papa sourit. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7027,6 +7089,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7196,6 +7259,7 @@
 papa|Je suis là. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7385,6 +7449,11 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -7554,6 +7623,7 @@
           <t>narrateur|Zoé a choisi le livre. Puis une pomme. Puis le chat. Une cloche tinte, tout loin. Zoé essuie ses mains. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7721,6 +7791,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7888,6 +7959,11 @@
           <t>narrateur|Zoé s'arrête près de le chien. une pomme est rangé. Le savon sent bon. Zoé marche près de papa. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8055,6 +8131,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8222,6 +8299,7 @@
           <t>narrateur|Zoé se souvient de le livre. Et de une pomme. Et de la poule. Une tasse cliquette. Zoé range encore un peu, près de papa. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8389,6 +8467,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8557,6 +8636,7 @@
 papa|Merci de raconter. Papa reste tout près. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8746,6 +8826,11 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -8915,6 +9000,7 @@
           <t>narrateur|Avec le chat. Après un yaourt. Près de le livre. Zoé s'arrête. On souffle doucement. Zoé pose un yaourt à sa place. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9082,6 +9168,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9249,6 +9336,11 @@
           <t>narrateur|Zoé range un yaourt. le chien reste près de le livre. Un galet est encore chaud. Zoé tend le chien à maman. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9416,6 +9508,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9585,6 +9678,7 @@
 narrateur|Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9752,6 +9846,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9920,6 +10015,7 @@
 papa|Merci de raconter. Papa montre le geste, lentement. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10109,6 +10205,11 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -10278,6 +10379,7 @@
           <t>narrateur|Zoé rejoint le chat. un morceau de pain est rangé. le livre est fini. On se tient la main. Zoé range la tasse. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10445,6 +10547,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10612,6 +10715,11 @@
           <t>narrateur|Près de le chien. Zoé pose un morceau de pain. le livre est derrière. On rit un peu. Zoé ferme le sac. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10779,6 +10887,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10946,6 +11055,7 @@
           <t>narrateur|Zoé montre la poule. Papa a vu le livre. Et un morceau de pain. La lumière est claire. Zoé serre la main de papa. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11113,6 +11223,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11281,6 +11392,7 @@
 papa|Merci de raconter. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11464,6 +11576,7 @@
           <t>narrateur|On cache, ou on raconte ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11635,6 +11748,7 @@
           <t>narrateur|Oui. On raconte à papa ou maman. Zoé hoche la tête. On continue, avec papa. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11826,6 +11940,7 @@
           <t>narrateur|On peut prendre une pomme, un yaourt, ou un morceau de pain.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11994,6 +12109,7 @@
 papa|Je suis là. Papa reste tout près. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12183,6 +12299,11 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -12352,6 +12473,7 @@
           <t>narrateur|Zoé a choisi la dînette. Puis une pomme. Puis le chat. Le vent est doux. Zoé ferme la porte, tout doux. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12519,6 +12641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12686,6 +12809,11 @@
           <t>narrateur|Zoé s'arrête près de le chien. une pomme est rangé. Une feuille tombe. Zoé prend la main de papa. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12853,6 +12981,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13020,6 +13149,7 @@
           <t>narrateur|Zoé se souvient de la dînette. Et de une pomme. Et de la poule. Une chaussette est encore sablée. Zoé répète tout bas le geste. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13187,6 +13317,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13355,6 +13486,7 @@
 papa|Je suis là. Papa montre le geste, lentement. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13544,6 +13676,11 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -13713,6 +13850,7 @@
           <t>narrateur|Avec le chat. Après un yaourt. Près de la dînette. Zoé s'arrête. On attend son tour. Zoé montre le chat à papa. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13880,6 +14018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14047,6 +14186,11 @@
           <t>narrateur|Zoé range un yaourt. le chien reste près de la dînette. Un vélo passe au loin. Zoé écoute papa encore une fois. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14214,6 +14358,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14381,6 +14526,7 @@
           <t>narrateur|La poule est là. un yaourt aussi. la dînette reste dans le souvenir. On range un objet. Zoé enfile ses chaussons. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14548,6 +14694,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14717,6 +14864,7 @@
 papa|Je suis là. On raconte à papa ou maman ce qui s'est passé.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14906,6 +15054,11 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -15075,6 +15228,7 @@
           <t>narrateur|Zoé rejoint le chat. un morceau de pain est rangé. la dînette est fini. L'eau coule, tout petit bruit. Zoé raccroche un linge. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15242,6 +15396,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15409,6 +15564,11 @@
           <t>narrateur|Près de le chien. Zoé pose un morceau de pain. la dînette est derrière. Un ballon s'immobilise. Zoé dit merci à papa. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15576,6 +15736,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15743,6 +15904,7 @@
           <t>narrateur|Zoé montre la poule. Papa a vu la dînette. Et un morceau de pain. Un crochet tient bien le manteau. Zoé chuchote : c'est fini. On raconte à papa ou maman ce qui s'est passé. On raconte. On va vers papa ou maman. Zoé dit merci à papa.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15910,6 +16072,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15928,7 +16091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15952,6 +16115,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15966,7 +16143,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16153,6 +16330,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
